--- a/construction_template/data/templates_blank/review_control.xlsx
+++ b/construction_template/data/templates_blank/review_control.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="67">
   <si>
-    <t xml:space="preserve">任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">材料設備送審管制總表</t>
@@ -39,7 +39,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工程名稱：士林區通河東街</t>
+      <t xml:space="preserve">工程名稱：</t>
     </r>
     <r>
       <rPr>
@@ -49,7 +49,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve"/>
     </r>
     <r>
       <rPr>
@@ -58,7 +58,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">段排水改善工程</t>
+      <t xml:space="preserve"/>
     </r>
   </si>
   <si>
@@ -79,14 +79,14 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">H-111-04-111056</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">監造單位：任泰技術顧問有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工廠商：安宏營造有限公司</t>
+      <t xml:space="preserve"/>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">監造單位：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工廠商：</t>
   </si>
   <si>
     <t xml:space="preserve">項次</t>

--- a/construction_template/data/templates_blank/review_control.xlsx
+++ b/construction_template/data/templates_blank/review_control.xlsx
@@ -1203,7 +1203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF99CC00"/>
     <pageSetUpPr fitToPage="false"/>
@@ -1403,7 +1403,7 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
         <v>26</v>
@@ -1449,7 +1449,7 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1497,7 +1497,7 @@
       <c r="O12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
         <v>35</v>
@@ -1543,7 +1543,7 @@
       <c r="O14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="8" t="s">
         <v>37</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="O16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
         <v>41</v>
@@ -1637,7 +1637,7 @@
       <c r="O18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="8" t="s">
         <v>43</v>
       </c>
@@ -1683,7 +1683,7 @@
       <c r="O20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
         <v>47</v>
@@ -1729,7 +1729,7 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
         <v>50</v>
@@ -1779,7 +1779,7 @@
       <c r="P24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
         <v>54</v>
@@ -1825,7 +1825,7 @@
       <c r="O26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
         <v>57</v>
@@ -1873,7 +1873,7 @@
       <c r="P28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n"/>
+      <c r="A29" s="7"/>
       <c r="B29" s="17"/>
       <c r="C29" s="9"/>
       <c r="D29" s="7"/>
@@ -2087,7 +2087,7 @@
       <c r="N38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
       <c r="D39" s="7"/>
@@ -2119,7 +2119,7 @@
       <c r="N40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
       <c r="D41" s="7"/>
@@ -2151,7 +2151,7 @@
       <c r="N42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="17"/>
       <c r="C43" s="9"/>
       <c r="D43" s="7"/>
@@ -2183,7 +2183,7 @@
       <c r="N44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="17"/>
       <c r="C45" s="9"/>
       <c r="D45" s="7"/>
@@ -2215,7 +2215,7 @@
       <c r="N46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="17"/>
       <c r="C47" s="9"/>
       <c r="D47" s="7"/>
@@ -2247,7 +2247,7 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="17"/>
       <c r="C49" s="9"/>
       <c r="D49" s="7"/>
@@ -2279,7 +2279,7 @@
       <c r="N50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="17"/>
       <c r="C51" s="9"/>
       <c r="D51" s="7"/>
@@ -2311,7 +2311,7 @@
       <c r="N52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n"/>
+      <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
       <c r="D53" s="7"/>
@@ -2343,7 +2343,7 @@
       <c r="N54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n"/>
+      <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
       <c r="D55" s="7"/>
@@ -2376,7 +2376,7 @@
       <c r="P56" s="28"/>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n"/>
+      <c r="A57" s="7"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
       <c r="D57" s="7"/>
@@ -2408,7 +2408,7 @@
       <c r="N58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n"/>
+      <c r="A59" s="7"/>
       <c r="B59" s="17"/>
       <c r="C59" s="9"/>
       <c r="D59" s="7"/>
@@ -2440,7 +2440,7 @@
       <c r="N60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n"/>
+      <c r="A61" s="7"/>
       <c r="B61" s="17"/>
       <c r="C61" s="9"/>
       <c r="D61" s="7"/>
@@ -2472,7 +2472,7 @@
       <c r="N62" s="12"/>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n"/>
+      <c r="A63" s="7"/>
       <c r="B63" s="17"/>
       <c r="C63" s="9"/>
       <c r="D63" s="7"/>
@@ -2504,7 +2504,7 @@
       <c r="N64" s="12"/>
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n"/>
+      <c r="A65" s="7"/>
       <c r="B65" s="17"/>
       <c r="C65" s="9"/>
       <c r="D65" s="7"/>
@@ -2536,7 +2536,7 @@
       <c r="N66" s="12"/>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n"/>
+      <c r="A67" s="7"/>
       <c r="B67" s="17"/>
       <c r="C67" s="9"/>
       <c r="D67" s="7"/>
@@ -2568,7 +2568,7 @@
       <c r="N68" s="12"/>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n"/>
+      <c r="A69" s="7"/>
       <c r="B69" s="17"/>
       <c r="C69" s="9"/>
       <c r="D69" s="7"/>
@@ -2600,7 +2600,7 @@
       <c r="N70" s="12"/>
     </row>
     <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n"/>
+      <c r="A71" s="7"/>
       <c r="B71" s="17"/>
       <c r="C71" s="9"/>
       <c r="D71" s="7"/>
@@ -2812,7 +2812,7 @@
       <c r="N80" s="33"/>
     </row>
     <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35" t="n"/>
+      <c r="A81" s="35"/>
       <c r="B81" s="36"/>
       <c r="C81" s="37"/>
       <c r="D81" s="35"/>
@@ -2844,7 +2844,7 @@
       <c r="N82" s="40"/>
     </row>
     <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="35" t="n"/>
+      <c r="A83" s="35"/>
       <c r="B83" s="36"/>
       <c r="C83" s="37"/>
       <c r="D83" s="35"/>
@@ -2876,7 +2876,7 @@
       <c r="N84" s="40"/>
     </row>
     <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="35" t="n"/>
+      <c r="A85" s="35"/>
       <c r="B85" s="36"/>
       <c r="C85" s="37"/>
       <c r="D85" s="35"/>
@@ -2908,7 +2908,7 @@
       <c r="N86" s="40"/>
     </row>
     <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="35" t="n"/>
+      <c r="A87" s="35"/>
       <c r="B87" s="36"/>
       <c r="C87" s="37"/>
       <c r="D87" s="35"/>
@@ -2940,7 +2940,7 @@
       <c r="N88" s="40"/>
     </row>
     <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="35" t="n"/>
+      <c r="A89" s="35"/>
       <c r="B89" s="36"/>
       <c r="C89" s="37"/>
       <c r="D89" s="35"/>

--- a/construction_template/data/templates_blank/review_control.xlsx
+++ b/construction_template/data/templates_blank/review_control.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="67">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">材料設備送審管制總表</t>
@@ -49,7 +49,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
     <r>
       <rPr>
@@ -58,7 +58,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>
@@ -79,7 +79,7 @@
         <family val="4"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve"/>
+      <t/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/review_control.xlsx
+++ b/construction_template/data/templates_blank/review_control.xlsx
@@ -41,16 +41,8 @@
       </rPr>
       <t xml:space="preserve">工程名稱：</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
-    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -58,28 +50,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">契約編號：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t/>
     </r>
   </si>
   <si>

--- a/construction_template/data/templates_blank/review_control.xlsx
+++ b/construction_template/data/templates_blank/review_control.xlsx
@@ -36,7 +36,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">工程名稱：</t>
@@ -47,7 +47,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">契約編號：</t>
@@ -72,7 +72,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是否取樣試驗</t>
@@ -89,7 +89,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">是ˇ、否 </t>
@@ -123,7 +123,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">備註</t>
@@ -140,7 +140,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">歸檔編號</t>
@@ -177,7 +177,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">材料</t>
@@ -194,7 +194,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">設備</t>
@@ -211,7 +211,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">名稱</t>
@@ -237,7 +237,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">該作業項目預定施工前</t>
@@ -256,7 +256,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日</t>
@@ -278,7 +278,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -302,7 +302,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">該作業項目預定施工前</t>
@@ -321,7 +321,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日</t>
@@ -348,7 +348,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">孔</t>
@@ -370,7 +370,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -411,7 +411,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">控制性低強度回填材料</t>
@@ -439,7 +439,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、</t>
@@ -469,7 +469,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組
@@ -489,7 +489,7 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">組</t>
@@ -525,7 +525,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">支</t>
@@ -585,7 +585,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應依契約之「材料、設備檢（試）驗一覽表」將資料填入，以預為準備材料設備送審事宜，並作為監造單位管制各項材料設備送審期程，且需納入結算書陳核。</t>
@@ -606,7 +606,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應將本表於開工報核時檢附提供予監造單位，監造單位報核開工時應檢附本表。</t>
@@ -627,7 +627,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
+        <rFont val="標楷體"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">施工廠商應於開工後適時更新本表，並提送監造單位審核，以確認各項材料設備送審期程是否符合時程。</t>
@@ -682,13 +682,13 @@
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -700,12 +700,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -730,7 +730,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
@@ -743,13 +743,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="標楷體"/>
       <family val="2"/>
     </font>
     <font>
